--- a/medford_istochniki_bespereboynogo_pitaniya.xlsx
+++ b/medford_istochniki_bespereboynogo_pitaniya.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Какие бывают источники бесперебойного питания?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>istochniki_bespereboynogo_pitaniya</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Что такое ИБП в медицине?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>istochniki_bespereboynogo_pitaniya</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>

--- a/medford_istochniki_bespereboynogo_pitaniya.xlsx
+++ b/medford_istochniki_bespereboynogo_pitaniya.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Источники бесперебойного питания для оснащения клиник и медицинских учреждений. В каталоге представлено 1 позиций.</t>
+          <t>Источники бесперебойного питания для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_istochniki_bespereboynogo_pitaniya.xlsx
+++ b/medford_istochniki_bespereboynogo_pitaniya.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать источники бесперебойного питания для клиники?</t>
+          <t>Какой ИБП нужен для УЗИ-аппарата?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Активная мощность). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Для УЗИ-аппарата профильные источники рекомендуют online-ИБП с двойным преобразованием и чистой синусоидой на выходе. Такая топология переключается на батарею без задержки и защищает чувствительные платы сканера от скачков напряжения. Мощность подбирают по паспорту аппарата с запасом 20–30%, для кабинета обычно 1–3 кВт.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какие бывают типы ИБП?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Различают три основных типа: резервные (off-line), которые переключаются на батарею с задержкой; линейно-интерактивные со стабилизацией напряжения, но тоже с задержкой переключения; и online с двойным преобразованием, работающие через инвертор без разрыва питания. Для чувствительного диагностического оборудования, включая УЗИ, рекомендуется online-топология.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Что такое ИБП в медицине?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>В медицине ИБП обеспечивает бесперебойное питание оборудования при отключениях и перепадах напряжения. Обычно его рассчитывают на 10–30 минут автономной работы — этого достаточно, чтобы корректно завершить исследование или процедуру, сохранить данные пациента и при необходимости дождаться запуска резервного генератора.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Почему для УЗИ нужна чистая синусоида?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>УЗИ-сканер содержит чувствительную электронику, которую ступенчатый (аппроксимированный) выходной сигнал может повредить. Чистая синусоида повторяет форму сетевого напряжения без искажений, поэтому питание остаётся безопасным для плат. Именно поэтому для диагностического оборудования выбирают online-ИБП с синусоидальным выходом.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Как рассчитать мощность ИБП?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Мощность ИБП рассчитывают по паспортной потребляемой мощности УЗИ-аппарата, добавляя запас 20–30% на пиковые нагрузки. Для типового кабинета это обычно 1–3 кВт (1000–3000 ВА). Недостаточная мощность приводит к перегрузке и отключению, избыточная — к лишним затратам, поэтому расчёт ведут по документации.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Какие бывают источники бесперебойного питания?</t>
+          <t>Что нельзя подключать к ИБП?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>К ИБП не подключают нагрузку, превышающую его мощность, а также устройства, профиль потребления которых несовместим с конкретной моделью. Перегрузка сокращает срок службы и снижает надёжность защиты. Перечень ограничений уточняют по инструкции производителя, поскольку он зависит от типа и мощности конкретного ИБП.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Что такое ИБП в медицине?</t>
+          <t>Сколько работает ИБП без сети?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Время автономной работы зависит от ёмкости батарей и мощности подключённой нагрузки: чем больше нагрузка, тем меньше время. В медицине обычно ориентируются на 10–30 минут, достаточных для корректного завершения исследования. Точное время рассчитывают под конкретный аппарат и требования кабинета.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Как часто менять батареи ИБП?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Аккумуляторы ИБП — расходный элемент, их ёмкость со временем снижается, поэтому периодически требуется замена. Конкретный срок зависит от модели, условий эксплуатации и температуры. Заранее уточняют доступность сменных батарей и сервис, чтобы плановая замена не прерывала работу диагностического кабинета.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>istochniki_bespereboynogo_pitaniya</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Источники бесперебойного питания для оснащения клиник и медицинских учреждений.</t>
+          <t>Источники бесперебойного питания защищают УЗИ-аппараты от отключений электричества и скачков напряжения. В категории представлен ИБП Ippon Innova G2 1000 с активной мощностью 900 Вт. Для ультразвукового оборудования профильные источники рекомендуют использовать online-ИБП с двойным преобразованием: они выдают чистую синусоиду и переключаются на батареи без задержки. Для типового медицинского кабинета обычно подбирают однофазные приборы мощностью от 1 до 3 кВт с запасом по нагрузке 20–30% и автономией порядка 10–30 минут.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы ИБП и пригодность для УЗИ</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2716,7 +2754,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое источники бесперебойного питания</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -2939,48 +2977,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы ИБП и пригодность для УЗИ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип ИБП</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Как работает</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Активная мощность</t>
+          <t>Пригодность для УЗИ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Источник бесперебойного питания Ippon Innova G2 1000</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Резервный (off-line)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>питание от сети, при сбое переключение на батарею с задержкой</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>900 Вт</t>
+          <t>недостаточно</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Линейно-интерактивный</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>стабилизация напряжения, есть задержка переключения</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ограниченно</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Online (двойное преобразование)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>постоянная работа через инвертор, без задержки, чистая синусоида</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>рекомендуется</t>
         </is>
       </c>
     </row>
@@ -2998,7 +3074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3324,12 +3400,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите мощность аппарата</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается источники бесперебойного питания: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала смотрят паспортную потребляемую мощность УЗИ-сканера. От неё считают требуемую мощность ИБП с запасом 20–30%, чтобы избежать перегрузки при пиковых нагрузках. Для типового кабинета это обычно диапазон 1–3 кВт (1000–3000 ВА). Расчёт ведут по паспорту, а не по приблизительной оценке.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3369,12 +3445,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите online-топологию</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Для УЗИ профильные источники рекомендуют online-ИБП с двойным преобразованием. Он постоянно питает нагрузку через инвертор, поэтому переключение на батарею происходит без задержки, а выходное напряжение очищается от скачков. Резервные и линейно-интерактивные модели для чувствительной диагностической электроники подходят хуже.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3414,12 +3490,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте форму сигнала</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Активная мощность. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>На выходе ИБП для УЗИ должна быть чистая синусоида без искажений: аппроксимированный (ступенчатый) сигнал способен навредить чувствительным платам сканера. Форму выходного сигнала уточняют по паспорту конкретной модели. Это требование считают обязательным для медицинского диагностического оборудования, а не желательной опцией.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3459,12 +3535,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Рассчитайте время автономии</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Определяют, сколько времени нужно на корректное завершение исследования и сохранение данных при отключении. В медицине обычно достаточно 10–30 минут — этого хватает, чтобы завершить процедуру или дождаться запуска резервного генератора. Требуемую автономию согласуют с мощностью нагрузки, поскольку они связаны.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3504,12 +3580,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите фазность и подключение</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Для кабинета с одним аппаратом обычно берут однофазный ИБП. Проверяют тип розеток и разъёмов, чтобы подключение соответствовало сети и оборудованию. Заранее уточняют, какая нагрузка будет подключена к ИБП, и не превышает ли она его мощность — перегрузка сокращает срок службы и надёжность.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3549,12 +3625,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Согласуйте сервис и замену батарей</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Батареи — расходуемый элемент ИБП, их ресурс со временем снижается. Заранее уточняют доступность сменных аккумуляторов, условия гарантии и сервис. Для непрерывной работы кабинета важно, чтобы замена батарей и обслуживание проводились планово и не приводили к длительным простоям диагностики.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3604,7 +3680,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Источники бесперебойного питания подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на активная мощность, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Для УЗИ-сканера важна не столько ёмкость батарей, сколько тип ИБП и форма выходного сигнала. Online-топология с двойным преобразованием и чистой синусоидой защищает чувствительную электронику от скачков и переключается без разрыва питания. Мощность считают по паспорту аппарата с запасом, а не «на глаз»: недобор приведёт к перегрузке, избыточный запас — к лишним затратам. Автономия нужна не на часы работы, а на корректное завершение исследования.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3888,13 +3964,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое источники бесперебойного питания</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Источники бесперебойного питания — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>ИБП для УЗИ-аппарата — устройство, которое защищает сканер от внезапных отключений электричества и перепадов напряжения. Профильные источники сходятся в том, что для УЗИ подходит online-ИБП с двойным преобразованием: он постоянно питает нагрузку через инвертор, выдаёт чистую синусоиду и переключается на батарею без задержки, оберегая чувствительные платы. Мощность подбирают по паспорту аппарата с запасом 20–30%, для кабинета это обычно 1–3 кВт (1000–3000 ВА). Автономии в 10–30 минут хватает, чтобы корректно завершить исследование и сохранить данные пациента.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3931,13 +4007,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>ИБП для УЗИ: зачем нужен</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Активная мощность), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Источник бесперебойного питания защищает УЗИ-аппарат от внезапных отключений электричества и перепадов напряжения, которые встречаются в электросетях и опасны для чувствительной электроники. ИБП обеспечивает время на корректное завершение исследования и сохранение данных пациента, а также сглаживает скачки напряжения, продлевая ресурс дорогостоящего сканера.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3974,13 +4050,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Почему online-топология</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Для УЗИ профильные источники рекомендуют online-ИБП с двойным преобразованием. В отличие от резервных и линейно-интерактивных моделей, он постоянно питает нагрузку через инвертор и переключается на батарею без задержки, а на выходе даёт чистую синусоиду. Это защищает платы сканера от искажений сигнала и кратковременных провалов питания.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4017,13 +4093,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Как подобрать мощность и автономию</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Мощность ИБП рассчитывают по паспорту УЗИ-аппарата с запасом 20–30%; для кабинета это обычно 1–3 кВт (1000–3000 ВА). Автономию подбирают под задачу: в медицине достаточно 10–30 минут, чтобы завершить исследование и сохранить данные. Мощность и время автономии связаны, поэтому их согласуют вместе, а не по отдельности.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4040,6 +4116,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Модель в категории</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>В категории представлен ИБП Ippon Innova G2 1000 с активной мощностью 900 Вт. Как и для любого источника питания под УЗИ, при подборе ориентируются на паспортную мощность конкретного сканера, форму выходного сигнала и требуемую автономию. Дополнительно учитывают доступность сменных батарей и условия сервисного обслуживания.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>istochniki_bespereboynogo_pitaniya</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
